--- a/other/vacuum_instrumentation_bundle_v2/bom/BOM (version 1).xlsx
+++ b/other/vacuum_instrumentation_bundle_v2/bom/BOM (version 1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aiden\Documents\GitHub\coldex-instrumentation\other\vacuum_instrumentation_bundle_v2\bom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33223573-B126-4280-A759-674C95EC1700}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0419E99-C922-4DDC-B0B0-2C5DE40F7E0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="32250" yWindow="0" windowWidth="19350" windowHeight="21000" activeTab="1" xr2:uid="{64365B26-9AB1-4F2A-B9FA-C5EB43087255}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="178">
   <si>
     <t>Group</t>
   </si>
@@ -540,6 +540,22 @@
   </si>
   <si>
     <t>t-slot mounting</t>
+  </si>
+  <si>
+    <t>18-8 Stainless Steel Low-Profile Socket Head Screws with Hex Drive, M6 x 1 mm Thread, 16 mm Long</t>
+  </si>
+  <si>
+    <t>https://www.mcmaster.com/92855A616/</t>
+  </si>
+  <si>
+    <t>Moisture-Resistant Cushioning Washer
+for 1/4" Screw Size, 0.257" ID, 0.5" OD</t>
+  </si>
+  <si>
+    <t>https://www.mcmaster.com/93650A145/</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/Anker-Transfer-Ultra-Slim-Charging-Supported/dp/B07L32B9C2/ref=sr_1_2?crid=2VOD9SFPCF44L&amp;dib=eyJ2IjoiMSJ9.lX3Oa0Sl6oY0sH5jggB4hndDACMujmEemxqr81Mhmv_qf_lht7oWL4rV6gLk5CEPt-Oi7MdzpaDOSACxXl95H-bXNJD9zI02BKaA4uSjzGkWPsST9s-1mz5I5j8X496G13TfBnsPCvMX_H04uwd0jPQrv9tXXUb9HJ77VHN1XalMCwDYh_jTpkT1HVOKWLeYmPGj5aCYDCqJCeFaeNExk3yHF4hBIhCjhyG6EVu8CUE.JXjleQbUHYKjRRoTVu8rZDu0P0YaVTncGOFQJ4WWNS4&amp;dib_tag=se&amp;keywords=usb%2Bsplitter&amp;qid=1789590684&amp;sprefix=usb%2Bsplitt%2Caps%2C206&amp;sr=8-2&amp;th=1</t>
   </si>
 </sst>
 </file>
@@ -2315,7 +2331,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53AE2797-3CBB-4F04-BC2E-DCAE66658ABF}">
-  <dimension ref="A1:N35"/>
+  <dimension ref="A1:N37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.28515625" style="2" customWidth="1"/>
@@ -2982,8 +2998,8 @@
       <c r="I19" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="K19" s="3" t="s">
-        <v>144</v>
+      <c r="K19" s="4" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
@@ -3051,6 +3067,9 @@
       <c r="F24" s="8" t="s">
         <v>169</v>
       </c>
+      <c r="I24" s="3" t="s">
+        <v>172</v>
+      </c>
       <c r="K24" s="4" t="s">
         <v>167</v>
       </c>
@@ -3069,59 +3088,84 @@
         <v>170</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="F26" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="K26" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>148</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>13</v>
+        <v>168</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="K27" s="4" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="F32" s="2" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="33" spans="6:11" x14ac:dyDescent="0.25">
-      <c r="F33" s="2" t="s">
-        <v>162</v>
+      <c r="B28" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="34" spans="6:11" x14ac:dyDescent="0.25">
       <c r="F34" s="2" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
     </row>
     <row r="35" spans="6:11" x14ac:dyDescent="0.25">
       <c r="F35" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="36" spans="6:11" x14ac:dyDescent="0.25">
+      <c r="F36" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="37" spans="6:11" x14ac:dyDescent="0.25">
+      <c r="F37" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="H35" s="5">
+      <c r="H37" s="5">
         <v>4.04</v>
       </c>
-      <c r="I35" s="3" t="s">
+      <c r="I37" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="K35" s="4" t="s">
+      <c r="K37" s="4" t="s">
         <v>164</v>
       </c>
     </row>
@@ -3142,10 +3186,13 @@
     <hyperlink ref="K16" r:id="rId13" xr:uid="{65A058D8-32A6-4710-9357-F9CD514C8F80}"/>
     <hyperlink ref="K17" r:id="rId14" display="https://www.mouser.com/en/ProductDetail/MEAN-WELL/HDR-150-24?qs=PqoDHHvF64%2FLzUHzMPaPtg%3D%3D&amp;utm_id=22522039646&amp;utm_source=google&amp;utm_medium=cpc&amp;utm_marketing_tactic=amercorp&amp;gad_source=1&amp;gad_campaignid=22525648075&amp;gclid=CjwKCAjwwfnUBhAtEiwAfQpAYs2He3P_bqoxDWWJgTUTE2_z-GCNm4llusVgJ-sLg-_hmyQJaYv0YhoCuksQAvD_BwE" xr:uid="{1196B434-7237-448E-A161-99C584231C79}"/>
     <hyperlink ref="K21" r:id="rId15" display="https://www.mouser.com/en/ProductDetail/MEAN-WELL/TS35-75-200?qs=1Kr7Jg1SGW8uBOHr%252BMBvyw%3D%3D&amp;mgh=1&amp;utm_id=23556925407&amp;utm_source=google&amp;utm_medium=cpc&amp;utm_marketing_tactic=amercorp&amp;gad_source=1&amp;gad_campaignid=23566852966&amp;gclid=CjwKCAjwwfnUBhAtEiwAfQpAYhRMq_8MhYCrO-MBs57myzAqbuJo0kw7SHUGX5r1NrkjOu9mI6x9exoCdeQQAvD_BwE" xr:uid="{11107530-A842-44F7-8A59-5D0F37296200}"/>
-    <hyperlink ref="K35" r:id="rId16" xr:uid="{24E454FC-43DE-4D41-804F-31032A037DB4}"/>
+    <hyperlink ref="K37" r:id="rId16" xr:uid="{24E454FC-43DE-4D41-804F-31032A037DB4}"/>
     <hyperlink ref="K24" r:id="rId17" xr:uid="{327F2AB3-3A76-4E6F-A5D2-9AE20EAA33C7}"/>
+    <hyperlink ref="K26" r:id="rId18" xr:uid="{6917B20A-4742-4329-914B-BCA0C2548D5C}"/>
+    <hyperlink ref="K27" r:id="rId19" xr:uid="{24BEDF8D-7C4E-43F4-B325-B183B9EB4D81}"/>
+    <hyperlink ref="K19" r:id="rId20" display="https://www.amazon.com/Anker-Transfer-Ultra-Slim-Charging-Supported/dp/B07L32B9C2/ref=sr_1_2?crid=2VOD9SFPCF44L&amp;dib=eyJ2IjoiMSJ9.lX3Oa0Sl6oY0sH5jggB4hndDACMujmEemxqr81Mhmv_qf_lht7oWL4rV6gLk5CEPt-Oi7MdzpaDOSACxXl95H-bXNJD9zI02BKaA4uSjzGkWPsST9s-1mz5I5j8X496G13TfBnsPCvMX_H04uwd0jPQrv9tXXUb9HJ77VHN1XalMCwDYh_jTpkT1HVOKWLeYmPGj5aCYDCqJCeFaeNExk3yHF4hBIhCjhyG6EVu8CUE.JXjleQbUHYKjRRoTVu8rZDu0P0YaVTncGOFQJ4WWNS4&amp;dib_tag=se&amp;keywords=usb%2Bsplitter&amp;qid=1789590684&amp;sprefix=usb%2Bsplitt%2Caps%2C206&amp;sr=8-2&amp;th=1" xr:uid="{A380380D-1FA7-4607-857B-53872FFB1480}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId18"/>
+  <pageSetup orientation="portrait" r:id="rId21"/>
 </worksheet>
 </file>
--- a/other/vacuum_instrumentation_bundle_v2/bom/BOM (version 1).xlsx
+++ b/other/vacuum_instrumentation_bundle_v2/bom/BOM (version 1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aiden\Documents\GitHub\coldex-instrumentation\other\vacuum_instrumentation_bundle_v2\bom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0419E99-C922-4DDC-B0B0-2C5DE40F7E0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E4DBCDE-0CD4-47A0-AD5D-4F4310BEAC5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="32250" yWindow="0" windowWidth="19350" windowHeight="21000" activeTab="1" xr2:uid="{64365B26-9AB1-4F2A-B9FA-C5EB43087255}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="176">
   <si>
     <t>Group</t>
   </si>
@@ -504,24 +504,6 @@
   </si>
   <si>
     <t xml:space="preserve">Nyloc nuts </t>
-  </si>
-  <si>
-    <t>M5 for din mounting</t>
-  </si>
-  <si>
-    <t>M5 bolt for din mounting</t>
-  </si>
-  <si>
-    <t>Din, plate mounting</t>
-  </si>
-  <si>
-    <t>https://www.mcmaster.com/90576A104/</t>
-  </si>
-  <si>
-    <t>M5 nylock nut</t>
-  </si>
-  <si>
-    <t>M5 bolt for plate assembly</t>
   </si>
   <si>
     <t>https://www.mcmaster.com/5537T97-5537T739/</t>
@@ -556,6 +538,19 @@
   </si>
   <si>
     <t>https://www.amazon.com/Anker-Transfer-Ultra-Slim-Charging-Supported/dp/B07L32B9C2/ref=sr_1_2?crid=2VOD9SFPCF44L&amp;dib=eyJ2IjoiMSJ9.lX3Oa0Sl6oY0sH5jggB4hndDACMujmEemxqr81Mhmv_qf_lht7oWL4rV6gLk5CEPt-Oi7MdzpaDOSACxXl95H-bXNJD9zI02BKaA4uSjzGkWPsST9s-1mz5I5j8X496G13TfBnsPCvMX_H04uwd0jPQrv9tXXUb9HJ77VHN1XalMCwDYh_jTpkT1HVOKWLeYmPGj5aCYDCqJCeFaeNExk3yHF4hBIhCjhyG6EVu8CUE.JXjleQbUHYKjRRoTVu8rZDu0P0YaVTncGOFQJ4WWNS4&amp;dib_tag=se&amp;keywords=usb%2Bsplitter&amp;qid=1789590684&amp;sprefix=usb%2Bsplitt%2Caps%2C206&amp;sr=8-2&amp;th=1</t>
+  </si>
+  <si>
+    <t>https://www.mcmaster.com/93650A320/</t>
+  </si>
+  <si>
+    <t>general acrylic mounting</t>
+  </si>
+  <si>
+    <t>Moisture-Resistant Cushioning Washer
+for Number 4 Screw Size, 0.125" ID, 0.250" OD</t>
+  </si>
+  <si>
+    <t>ea (10 pack)</t>
   </si>
 </sst>
 </file>
@@ -2336,7 +2331,7 @@
   <cols>
     <col min="1" max="1" width="21.28515625" style="2" customWidth="1"/>
     <col min="2" max="5" width="9.140625" style="2"/>
-    <col min="6" max="6" width="37.7109375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="42.140625" style="2" customWidth="1"/>
     <col min="7" max="7" width="9.5703125" style="2" customWidth="1"/>
     <col min="8" max="8" width="9.140625" style="5"/>
     <col min="9" max="9" width="39.140625" style="3" customWidth="1"/>
@@ -2419,7 +2414,7 @@
       <c r="J2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="4" t="s">
         <v>19</v>
       </c>
       <c r="M2" s="2" t="s">
@@ -2999,7 +2994,7 @@
         <v>143</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
@@ -3053,7 +3048,7 @@
         <v>148</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="C24" s="2">
         <v>4</v>
@@ -3065,13 +3060,13 @@
         <v>71</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="30" x14ac:dyDescent="0.25">
@@ -3079,24 +3074,24 @@
         <v>148</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="F26" s="8" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="30" x14ac:dyDescent="0.25">
@@ -3104,13 +3099,13 @@
         <v>148</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -3135,39 +3130,37 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
+    <row r="33" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="34" spans="6:11" x14ac:dyDescent="0.25">
-      <c r="F34" s="2" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="35" spans="6:11" x14ac:dyDescent="0.25">
-      <c r="F35" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="36" spans="6:11" x14ac:dyDescent="0.25">
-      <c r="F36" s="2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="37" spans="6:11" x14ac:dyDescent="0.25">
-      <c r="F37" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="H37" s="5">
-        <v>4.04</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="K37" s="4" t="s">
-        <v>164</v>
-      </c>
+      <c r="C33" s="2">
+        <v>2</v>
+      </c>
+      <c r="D33" s="2">
+        <v>2</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="H33" s="5">
+        <v>8.6</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="K33" s="4" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K37" s="4"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -3186,13 +3179,14 @@
     <hyperlink ref="K16" r:id="rId13" xr:uid="{65A058D8-32A6-4710-9357-F9CD514C8F80}"/>
     <hyperlink ref="K17" r:id="rId14" display="https://www.mouser.com/en/ProductDetail/MEAN-WELL/HDR-150-24?qs=PqoDHHvF64%2FLzUHzMPaPtg%3D%3D&amp;utm_id=22522039646&amp;utm_source=google&amp;utm_medium=cpc&amp;utm_marketing_tactic=amercorp&amp;gad_source=1&amp;gad_campaignid=22525648075&amp;gclid=CjwKCAjwwfnUBhAtEiwAfQpAYs2He3P_bqoxDWWJgTUTE2_z-GCNm4llusVgJ-sLg-_hmyQJaYv0YhoCuksQAvD_BwE" xr:uid="{1196B434-7237-448E-A161-99C584231C79}"/>
     <hyperlink ref="K21" r:id="rId15" display="https://www.mouser.com/en/ProductDetail/MEAN-WELL/TS35-75-200?qs=1Kr7Jg1SGW8uBOHr%252BMBvyw%3D%3D&amp;mgh=1&amp;utm_id=23556925407&amp;utm_source=google&amp;utm_medium=cpc&amp;utm_marketing_tactic=amercorp&amp;gad_source=1&amp;gad_campaignid=23566852966&amp;gclid=CjwKCAjwwfnUBhAtEiwAfQpAYhRMq_8MhYCrO-MBs57myzAqbuJo0kw7SHUGX5r1NrkjOu9mI6x9exoCdeQQAvD_BwE" xr:uid="{11107530-A842-44F7-8A59-5D0F37296200}"/>
-    <hyperlink ref="K37" r:id="rId16" xr:uid="{24E454FC-43DE-4D41-804F-31032A037DB4}"/>
-    <hyperlink ref="K24" r:id="rId17" xr:uid="{327F2AB3-3A76-4E6F-A5D2-9AE20EAA33C7}"/>
-    <hyperlink ref="K26" r:id="rId18" xr:uid="{6917B20A-4742-4329-914B-BCA0C2548D5C}"/>
-    <hyperlink ref="K27" r:id="rId19" xr:uid="{24BEDF8D-7C4E-43F4-B325-B183B9EB4D81}"/>
-    <hyperlink ref="K19" r:id="rId20" display="https://www.amazon.com/Anker-Transfer-Ultra-Slim-Charging-Supported/dp/B07L32B9C2/ref=sr_1_2?crid=2VOD9SFPCF44L&amp;dib=eyJ2IjoiMSJ9.lX3Oa0Sl6oY0sH5jggB4hndDACMujmEemxqr81Mhmv_qf_lht7oWL4rV6gLk5CEPt-Oi7MdzpaDOSACxXl95H-bXNJD9zI02BKaA4uSjzGkWPsST9s-1mz5I5j8X496G13TfBnsPCvMX_H04uwd0jPQrv9tXXUb9HJ77VHN1XalMCwDYh_jTpkT1HVOKWLeYmPGj5aCYDCqJCeFaeNExk3yHF4hBIhCjhyG6EVu8CUE.JXjleQbUHYKjRRoTVu8rZDu0P0YaVTncGOFQJ4WWNS4&amp;dib_tag=se&amp;keywords=usb%2Bsplitter&amp;qid=1789590684&amp;sprefix=usb%2Bsplitt%2Caps%2C206&amp;sr=8-2&amp;th=1" xr:uid="{A380380D-1FA7-4607-857B-53872FFB1480}"/>
+    <hyperlink ref="K24" r:id="rId16" xr:uid="{327F2AB3-3A76-4E6F-A5D2-9AE20EAA33C7}"/>
+    <hyperlink ref="K26" r:id="rId17" xr:uid="{6917B20A-4742-4329-914B-BCA0C2548D5C}"/>
+    <hyperlink ref="K27" r:id="rId18" xr:uid="{24BEDF8D-7C4E-43F4-B325-B183B9EB4D81}"/>
+    <hyperlink ref="K19" r:id="rId19" display="https://www.amazon.com/Anker-Transfer-Ultra-Slim-Charging-Supported/dp/B07L32B9C2/ref=sr_1_2?crid=2VOD9SFPCF44L&amp;dib=eyJ2IjoiMSJ9.lX3Oa0Sl6oY0sH5jggB4hndDACMujmEemxqr81Mhmv_qf_lht7oWL4rV6gLk5CEPt-Oi7MdzpaDOSACxXl95H-bXNJD9zI02BKaA4uSjzGkWPsST9s-1mz5I5j8X496G13TfBnsPCvMX_H04uwd0jPQrv9tXXUb9HJ77VHN1XalMCwDYh_jTpkT1HVOKWLeYmPGj5aCYDCqJCeFaeNExk3yHF4hBIhCjhyG6EVu8CUE.JXjleQbUHYKjRRoTVu8rZDu0P0YaVTncGOFQJ4WWNS4&amp;dib_tag=se&amp;keywords=usb%2Bsplitter&amp;qid=1789590684&amp;sprefix=usb%2Bsplitt%2Caps%2C206&amp;sr=8-2&amp;th=1" xr:uid="{A380380D-1FA7-4607-857B-53872FFB1480}"/>
+    <hyperlink ref="K2" r:id="rId20" xr:uid="{56E55E87-D3D7-4114-B2AD-B89FADADB50F}"/>
+    <hyperlink ref="K33" r:id="rId21" xr:uid="{2F249DB4-CFC6-4095-8EA8-F19BDCB7AD80}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId21"/>
+  <pageSetup orientation="portrait" r:id="rId22"/>
 </worksheet>
 </file>
--- a/other/vacuum_instrumentation_bundle_v2/bom/BOM (version 1).xlsx
+++ b/other/vacuum_instrumentation_bundle_v2/bom/BOM (version 1).xlsx
@@ -8,20 +8,34 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aiden\Documents\GitHub\coldex-instrumentation\other\vacuum_instrumentation_bundle_v2\bom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E4DBCDE-0CD4-47A0-AD5D-4F4310BEAC5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{191951C3-3B69-401C-89FA-9664CB749EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32250" yWindow="0" windowWidth="19350" windowHeight="21000" activeTab="1" xr2:uid="{64365B26-9AB1-4F2A-B9FA-C5EB43087255}"/>
+    <workbookView xWindow="25800" yWindow="0" windowWidth="25800" windowHeight="21000" activeTab="1" xr2:uid="{64365B26-9AB1-4F2A-B9FA-C5EB43087255}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM" sheetId="1" r:id="rId1"/>
     <sheet name="BOM_revised" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="179">
   <si>
     <t>Group</t>
   </si>
@@ -551,6 +565,15 @@
   </si>
   <si>
     <t>ea (10 pack)</t>
+  </si>
+  <si>
+    <t>Nice to have items</t>
+  </si>
+  <si>
+    <t>80/20 handle for carrying</t>
+  </si>
+  <si>
+    <t>80/20 cable tie mounts</t>
   </si>
 </sst>
 </file>
@@ -1063,7 +1086,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
@@ -1081,6 +1104,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -3189,4 +3214,32 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId22"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53FFDAE8-D232-4FAD-9028-6E53C5768A44}">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="45.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/other/vacuum_instrumentation_bundle_v2/bom/BOM (version 1).xlsx
+++ b/other/vacuum_instrumentation_bundle_v2/bom/BOM (version 1).xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aiden\Documents\GitHub\coldex-instrumentation\other\vacuum_instrumentation_bundle_v2\bom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{191951C3-3B69-401C-89FA-9664CB749EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDC1D227-23D6-4071-83B9-EA8FEE212335}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25800" yWindow="0" windowWidth="25800" windowHeight="21000" activeTab="1" xr2:uid="{64365B26-9AB1-4F2A-B9FA-C5EB43087255}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="38700" windowHeight="15435" activeTab="3" xr2:uid="{64365B26-9AB1-4F2A-B9FA-C5EB43087255}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM" sheetId="1" r:id="rId1"/>
     <sheet name="BOM_revised" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1086,7 +1087,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
@@ -1105,7 +1106,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -3230,7 +3230,7 @@
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="A2" t="s">
         <v>177</v>
       </c>
     </row>
@@ -3242,4 +3242,13 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70DFDCB6-502F-43E3-A74A-BD92E08CFF1D}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>